--- a/delivery/documents/LDMT_JUNTOS_Final.xlsx
+++ b/delivery/documents/LDMT_JUNTOS_Final.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>MVP Final 1</t>
+          <t>MVP Final 2</t>
         </is>
       </c>
       <c r="G6" s="1"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Plataformas de descanso atravessaveis de baixo para cima; inimigo provoca recuperacao conservando estoque/torre.</t>
+          <t>Plataformas de descanso atravessaveis de baixo para cima; morte devolve ao checkpoint e remove blocos construidos de ambos somente na secao atual.</t>
         </is>
       </c>
       <c r="L11" s="11" t="str">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Recuperacao apos queda maior que 160 px; camera acompanha o jogador mais baixo.</t>
+          <t>Queda maior que 160 px limpa a secao do checkpoint, preserva estoque sem reembolso e mantem plataformas fixas/outras secoes; teste por IDs passou.</t>
         </is>
       </c>
       <c r="L12" s="11" t="str">

--- a/delivery/documents/LDMT_JUNTOS_Final.xlsx
+++ b/delivery/documents/LDMT_JUNTOS_Final.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>MVP Final 2</t>
+          <t>MVP Final 3</t>
         </is>
       </c>
       <c r="G6" s="1"/>
@@ -2846,12 +2846,12 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Prontidao conjunta</t>
+          <t>Selecionar modo/personagem</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Titulo e divindade visual; ambos confirmam.</t>
+          <t>Menu visual; ruinas, artefato e chamado divino sem palavras.</t>
         </is>
       </c>
       <c r="H9" s="12">
@@ -2866,7 +2866,11 @@
         <f t="shared" ref="J9:J38" si="0">IF(C9="","",IF(L9="Ready",H9+I9,NA()))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="10"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Revisao: arte simplificada aprovada; menu solo/coop e escolha do personagem no solo; abertura de tres momentos.</t>
+        </is>
+      </c>
       <c r="L9" s="11" t="str">
         <f>IF(C9="","",IF(COUNTIF('Level Map'!$B$9:$B$308,B9)=0,"Add map entries",IF(COUNTIFS('Level Map'!$B$9:$B$308,B9,'Level Map'!$J$9:$J$308,"&lt;&gt;Ready")&gt;0,"Fix map entries","Ready")))</f>
         <v>Ready</v>
@@ -3050,12 +3054,12 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Chegada dos dois</t>
+          <t>Chegada dos participantes</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Objetivo so conclui quando ambos estao no topo.</t>
+          <t>Todos os ativos pousam no topo: um no solo, dois no cooperativo.</t>
         </is>
       </c>
       <c r="H13" s="12">
@@ -3072,7 +3076,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Vitoria exige os dois pousados no topo; teste automatizado percorre as mesmas colisoes e entradas.</t>
+          <t>Testes Runner: coop e solo com cada personagem; coleta/construcao, topo e reinicio. Inativo nao joga.</t>
         </is>
       </c>
       <c r="L13" s="11" t="str">
@@ -4728,7 +4732,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Prontidao independente dos dois</t>
+          <t>Selecao de modo/personagem e abertura visual</t>
         </is>
       </c>
       <c r="G9" s="11" t="str">
@@ -5184,7 +5188,7 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Pouso de ambos</t>
+          <t>Pouso de todos os participantes ativos</t>
         </is>
       </c>
       <c r="G21" s="11" t="str">
